--- a/data/trans_camb/IP07_C13_R_2023-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_C13_R_2023-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.238720136396812</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.895870974068053</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-8.782302004926812</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-12.75632005134202</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-4.837511171143495</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-8.733573033092259</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-8.152285922727286</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-12.28342055192722</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-16.7719522212198</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-21.39612026461178</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-9.6465246429738</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-14.83495237884037</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>5.409212474042007</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.186678199156113</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.907214052127461</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-3.652014307599207</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.2993567054493648</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.7192984650239408</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.09630132548373593</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.380617744353087</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.4987712938288147</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.7244668030014226</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.321112785640463</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5797324008220867</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.4846610268209559</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.8389942846708167</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.7199045925910903</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5561912744769051</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8552997655187232</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.5904499994462213</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.078643289442914</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.08209948531544244</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.1190477554501617</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03471461848416296</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.008354118217393782</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1.512244988944414</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.840919646221347</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.43757795843706</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-8.869983083103413</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.553792957197388</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-8.499119026272728</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.858449129664575</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.94138895130005</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12.04873713573713</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-16.37145118038845</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-6.512636662481955</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-13.00408836144111</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>8.12842114996892</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-3.175588239801161</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.792997350075295</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-1.845962740718775</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.669970094301613</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-4.121607961325304</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.2025124658877937</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.9161025605140629</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.3068613386411283</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6133649725364889</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1402533942448031</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.7671744719936358</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5379434595276307</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.6680702864452471</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.9058020132161029</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4743688024702163</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9151544752672404</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.755984115052935</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.2925147422824121</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3150986900569502</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.06840406506383713</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4723024199707605</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.4811559903444734</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-5.06468622099826</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-12.02568547446296</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-8.296516400069077</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-14.69664285358138</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-6.535338900890532</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-13.43965838508806</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-13.53964578094287</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-19.9208561120613</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-17.01177215234683</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-23.11329149229763</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-13.08292615604336</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-19.26143762923234</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>3.19518266331897</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-5.952993689714341</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.753792471052965</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-6.003966052846849</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.5008008932840878</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-8.827954541973002</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.3864244795930244</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.9175334953530065</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.4691775511748957</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.831112068250469</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4288396897232852</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.8818913631338627</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.7472977223305728</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7731868959079233</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6867366147274302</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.9707366118987495</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.4130981869579168</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.4577837953675288</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.2170630512999566</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.2995990294177316</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.00877665628437815</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.6601591078645873</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-10.62310158382079</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-17.07645338809249</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.6154606108794716</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-3.416552500638819</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-5.197266085934771</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-10.01088635435616</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-24.74413393320685</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-30.76773155853135</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.421660069036438</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-12.32457033984104</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-14.74655514485347</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-18.62445199432223</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.307014400379519</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-6.70182236882432</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.442577942959865</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>4.948371744139559</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.663223732574426</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-4.010151989758493</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.55702432301492</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.8954070346540821</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.08619335901958169</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.4784776329975103</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.406641805224387</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.7832665928050897</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.8879369951636984</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.7997573890751645</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.941801672189593</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1206,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.3668275286334384</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.3580662956611415</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>0.4399971841028273</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.2770296145431461</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1232,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-2.200364323028579</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-10.06080019317295</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-6.274598372379482</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-10.96261863118856</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-4.196250612696732</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-10.6710053506341</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1258,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.274894886560602</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-13.13748453510728</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-11.10108381386392</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-15.23023700634941</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-7.269431617991502</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-13.25323434796466</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1284,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>2.490920843720656</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-6.750676016991858</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-2.512984537964011</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-6.532036843871373</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-1.141238591512861</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-7.833638640766432</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1310,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1839063235785264</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.8408811015613499</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.4101502231827244</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.7165909611110242</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3087349287842165</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.7851085125887617</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1336,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.452587357325459</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.9428948559407486</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.6057719090677656</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.8548060432214412</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.4707236499284618</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.8690476319808756</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1362,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2602118136863427</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.6660684219220878</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.1655985046462912</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.4662039017746957</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.08151407034218208</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.6454899821295641</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1390,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
